--- a/output/pdf_financials_xlsx/SGML.xlsx
+++ b/output/pdf_financials_xlsx/SGML.xlsx
@@ -5543,19 +5543,19 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.037585</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.037585</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.033975</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.033975</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.033975</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0.221244</v>
@@ -27578,7 +27578,11 @@
           <t>Share-based payment reserve 5</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -28098,7 +28102,11 @@
           <t>Share-based payment reserve 4</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -28739,7 +28747,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -29301,7 +29313,11 @@
           <t>Share-based payment reserve (Note 4) 37,585</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SGML.xlsx
+++ b/output/pdf_financials_xlsx/SGML.xlsx
@@ -1013,16 +1013,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00065</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000104</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001199</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000327</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1943,16 +1943,16 @@
         <v>-0.125449</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.060823</v>
+        <v>-0.061473</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.108089</v>
+        <v>-0.108193</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.109081</v>
+        <v>-0.11028</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.156436</v>
+        <v>-0.156763</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-8.665759</v>
@@ -2055,16 +2055,16 @@
         <v>-0.125449</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.060823</v>
+        <v>-0.061473</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.108089</v>
+        <v>-0.108193</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.109081</v>
+        <v>-0.11028</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.156436</v>
+        <v>-0.156763</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-8.655567</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.122814</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.062928</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.203385</v>
@@ -2349,7 +2349,7 @@
         <v>0.10364</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>13.543024</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>154.305</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.122814</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.062928</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.203385</v>
@@ -2457,7 +2457,7 @@
         <v>0.10364</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>13.543024</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>154.305</v>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.122814</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.063795</v>
+        <v>0.000867</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0.380225</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>14.046444</v>
+        <v>0.50342</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.8090000000000001</v>
@@ -7201,16 +7201,16 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.07184699999999999</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.035231</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.319</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -7253,16 +7253,16 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.07184699999999999</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.035231</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.319</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>0</v>
@@ -23105,7 +23105,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -27307,7 +27307,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -28842,7 +28842,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -40700,7 +40700,11 @@
           <t>Lease payments (note 11)</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -44015,7 +44019,11 @@
           <t>Lease payments (note 12 and 13)</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -49906,7 +49914,11 @@
           <t>General and administrative expenses 25.b</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr">
         <is>
           <t>-</t>
@@ -51350,7 +51362,11 @@
           <t>General and administrative expenses 25b</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -52420,7 +52436,11 @@
           <t>General and administrative expenses 25(b)</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -55846,7 +55866,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">

--- a/output/pdf_financials_xlsx/SGML.xlsx
+++ b/output/pdf_financials_xlsx/SGML.xlsx
@@ -6969,25 +6969,25 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.170455</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>0.254879</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>0.057531</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>0.0975</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>0</v>
@@ -46195,7 +46195,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -47896,7 +47900,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E443" t="inlineStr">
         <is>
           <t>-</t>
@@ -49004,7 +49012,11 @@
           <t>Issue of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E455" s="5" t="n">
         <v>0.1</v>
       </c>

--- a/output/pdf_financials_xlsx/SGML.xlsx
+++ b/output/pdf_financials_xlsx/SGML.xlsx
@@ -3574,13 +3574,13 @@
         <v>0</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>33.072</v>
       </c>
       <c r="M56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>251.414</v>
       </c>
       <c r="O56" s="3" t="n">
         <v>0</v>
@@ -4141,28 +4141,26 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.025066</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.007434</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.008361</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0105</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -4336,10 +4334,10 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.376</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>0</v>
@@ -4390,10 +4388,10 @@
         <v>2.68388</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.376</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>0</v>
@@ -4609,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>9.24</v>
+        <v>8.56</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>111.047</v>
@@ -4900,10 +4898,10 @@
         <v>0.1233551074331302</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.01051908578598393</v>
+        <v>0.01255259542892992</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.01632387797232204</v>
+        <v>0.02003757386431903</v>
       </c>
       <c r="N80" s="1" t="inlineStr">
         <is>
@@ -6496,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001145</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7762,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001145</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -7814,7 +7812,7 @@
         <v>-0.042489</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.104007</v>
+        <v>-0.105152</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.059886</v>
@@ -20854,7 +20852,11 @@
           <t>Lease liabilities (note 11)</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -49198,7 +49200,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
